--- a/dummy_input/AutostaffChubu_Model_Base.xlsx
+++ b/dummy_input/AutostaffChubu_Model_Base.xlsx
@@ -843,6 +843,19 @@
         <v>5500000</v>
       </c>
     </row>
+    <row r="22">
+      <c r="B22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>スポンサー提示EBITDA（速報・ティーザー記載）</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>1585000</v>
+      </c>
+    </row>
     <row r="24">
       <c r="B24" s="5" t="inlineStr">
         <is>
